--- a/incident_report_forms/030_cybersecurity_incident_form--incident_report_forms.xlsx
+++ b/incident_report_forms/030_cybersecurity_incident_form--incident_report_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>incident_form_page_1</t>
+          <t>incident_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Incident Report</t>
+          <t>Incident Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>incident_form_page_2</t>
+          <t>incident_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Breach Information</t>
+          <t>Type of Incident</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>incident_form_page_3</t>
+          <t>incident_impact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Response Information</t>
+          <t>Incident Impact</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,18 +579,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>incident_form_page_4</t>
+          <t>reporting_person</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remediation Information</t>
+          <t>Reporting Person</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,18 +602,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>incident_form_page_5</t>
+          <t>reporting_person_contact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Review and Submit</t>
+          <t>Reporting Person's Contact Info</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -625,41 +625,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>incident_form_page_6</t>
+          <t>affected_systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Breach Information</t>
+          <t>Affected Systems/Devices</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>incident_form_page_7</t>
+          <t>breach_details</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Response Information</t>
+          <t>Breach Details</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,18 +671,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>incident_form_page_8</t>
+          <t>response_actions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remediation Information</t>
+          <t>Response Actions Taken</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>incident_form_page_9</t>
+          <t>review_and_submit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -705,7 +705,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
